--- a/main/ig/observations-summary.xlsx
+++ b/main/ig/observations-summary.xlsx
@@ -89,33 +89,33 @@
     <t>Observation - FR Observation Birth Event Document</t>
   </si>
   <si>
-    <t>null#118215003</t>
+    <t>SNOMED CT#118215003</t>
+  </si>
+  <si>
+    <t>dateTimeĵ</t>
+  </si>
+  <si>
+    <t>fr-observation-blood-product-transfusion-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Blood Product Transfusion Document</t>
+  </si>
+  <si>
+    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-145</t>
+  </si>
+  <si>
+    <t>fr-observation-contra-indications-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Contra Indications Document</t>
+  </si>
+  <si>
+    <t>null#64100-1</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
-    <t>dateTimeĵ</t>
-  </si>
-  <si>
-    <t>fr-observation-blood-product-transfusion-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Blood Product Transfusion Document</t>
-  </si>
-  <si>
-    <t>null#MED-145</t>
-  </si>
-  <si>
-    <t>fr-observation-contra-indications-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Contra Indications Document</t>
-  </si>
-  <si>
-    <t>null#64100-1</t>
-  </si>
-  <si>
     <t>CodeableConceptĵ</t>
   </si>
   <si>
@@ -125,7 +125,7 @@
     <t>Observation - FR Observation Medical Summary Document</t>
   </si>
   <si>
-    <t>null#MED-142</t>
+    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-142</t>
   </si>
   <si>
     <t>stringĵ</t>
@@ -507,10 +507,10 @@
         <v>25</v>
       </c>
       <c r="F4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>27</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>13</v>
@@ -527,22 +527,22 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="C5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="C5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>30</v>
-      </c>
       <c r="F5" t="s" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>15</v>
@@ -562,22 +562,22 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B6" t="s" s="2">
+      <c r="C6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="C6" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s" s="2">
+      <c r="F6" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>26</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>15</v>
@@ -612,7 +612,7 @@
         <v>37</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>15</v>
@@ -717,10 +717,10 @@
         <v>47</v>
       </c>
       <c r="F10" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>27</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>48</v>
@@ -752,7 +752,7 @@
         <v>51</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>52</v>
@@ -790,7 +790,7 @@
         <v>13</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>22</v>
@@ -1000,7 +1000,7 @@
         <v>71</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>60</v>
@@ -1035,7 +1035,7 @@
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>13</v>
